--- a/ExcelData/GoibiboReport.xlsx
+++ b/ExcelData/GoibiboReport.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet_3" r:id="rId3" sheetId="1"/>
+    <sheet name="CabsList" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -150,6 +151,144 @@
   </si>
   <si>
     <t>Diwali Gift Card</t>
+  </si>
+  <si>
+    <t>Cab Name</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>Xylo, Ertiga</t>
+  </si>
+  <si>
+    <t>8752</t>
+  </si>
+  <si>
+    <t>4.3/5</t>
+  </si>
+  <si>
+    <t>9940</t>
+  </si>
+  <si>
+    <t>Toyota Innova</t>
+  </si>
+  <si>
+    <t>12500</t>
+  </si>
+  <si>
+    <t>NEW</t>
+  </si>
+  <si>
+    <t>Innova Crysta</t>
+  </si>
+  <si>
+    <t>14050</t>
+  </si>
+  <si>
+    <t>3.5/5</t>
+  </si>
+  <si>
+    <t>37625</t>
+  </si>
+  <si>
+    <t>4.5/5</t>
+  </si>
+  <si>
+    <t>51254</t>
+  </si>
+  <si>
+    <t>4.2/5</t>
+  </si>
+  <si>
+    <t>68233</t>
+  </si>
+  <si>
+    <t>4.1/5</t>
+  </si>
+  <si>
+    <t>Name = Xylo, Ertiga</t>
+  </si>
+  <si>
+    <t>Price = 58919</t>
+  </si>
+  <si>
+    <t>Rating = 4.1/5</t>
+  </si>
+  <si>
+    <t>Price = 63720</t>
+  </si>
+  <si>
+    <t>Rating = 4.5/5</t>
+  </si>
+  <si>
+    <t>Name = Innova Crysta</t>
+  </si>
+  <si>
+    <t>Price = 108432</t>
+  </si>
+  <si>
+    <t>Rating = 3.9/5</t>
+  </si>
+  <si>
+    <t>Price = 37625</t>
+  </si>
+  <si>
+    <t>Price = 51254</t>
+  </si>
+  <si>
+    <t>Rating = 4.2/5</t>
+  </si>
+  <si>
+    <t>Price = 68233</t>
+  </si>
+  <si>
+    <t>Name = WagonR, Swift</t>
+  </si>
+  <si>
+    <t>Price = 80454</t>
+  </si>
+  <si>
+    <t>Rating = 4/5</t>
+  </si>
+  <si>
+    <t>Price = 83503</t>
+  </si>
+  <si>
+    <t>Rating = 4.3/5</t>
+  </si>
+  <si>
+    <t>WagonR, Swift</t>
+  </si>
+  <si>
+    <t>80454</t>
+  </si>
+  <si>
+    <t>4/5</t>
+  </si>
+  <si>
+    <t>83503</t>
+  </si>
+  <si>
+    <t>9179</t>
+  </si>
+  <si>
+    <t>30108</t>
+  </si>
+  <si>
+    <t>32271</t>
+  </si>
+  <si>
+    <t>37965</t>
+  </si>
+  <si>
+    <t>52742</t>
+  </si>
+  <si>
+    <t>72424</t>
   </si>
 </sst>
 </file>
@@ -384,4 +523,70 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ExcelData/GoibiboReport.xlsx
+++ b/ExcelData/GoibiboReport.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Sheet_3" r:id="rId3" sheetId="1"/>
     <sheet name="CabsList" r:id="rId4" sheetId="2"/>
+    <sheet name="GiftCardsList" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -589,4 +590,198 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ExcelData/GoibiboReport.xlsx
+++ b/ExcelData/GoibiboReport.xlsx
@@ -7,14 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet_3" r:id="rId3" sheetId="1"/>
-    <sheet name="CabsList" r:id="rId4" sheetId="2"/>
-    <sheet name="GiftCardsList" r:id="rId5" sheetId="3"/>
+    <sheet name="GiftCardsList" r:id="rId5" sheetId="5"/>
+    <sheet name="CabsList" r:id="rId6" sheetId="6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="93">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>72424</t>
+  </si>
+  <si>
+    <t>120512</t>
   </si>
 </sst>
 </file>
@@ -526,7 +529,201 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -590,198 +787,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s" s="0">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>45</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/ExcelData/GoibiboReport.xlsx
+++ b/ExcelData/GoibiboReport.xlsx
@@ -7,14 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet_3" r:id="rId3" sheetId="1"/>
-    <sheet name="GiftCardsList" r:id="rId5" sheetId="5"/>
     <sheet name="CabsList" r:id="rId6" sheetId="6"/>
+    <sheet name="GiftCardsList" r:id="rId5" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="93">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -529,200 +529,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="B22" t="s" s="0">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>45</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:D4"/>
@@ -787,4 +593,198 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ExcelData/GoibiboReport.xlsx
+++ b/ExcelData/GoibiboReport.xlsx
@@ -13,15 +13,17 @@
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CheapestFlights" r:id="rId7" sheetId="12"/>
-    <sheet name="TimeBasedResults" r:id="rId6" sheetId="13"/>
+    <sheet name="CabsList" r:id="rId8" sheetId="18"/>
+    <sheet name="GiftCardsList" r:id="rId9" sheetId="19"/>
+    <sheet name="CheapestFlights" r:id="rId7" sheetId="20"/>
+    <sheet name="TimeBasedResults" r:id="rId10" sheetId="21"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2454" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2878" uniqueCount="114">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -258,6 +260,111 @@
   </si>
   <si>
     <t>Rs. 16,235</t>
+  </si>
+  <si>
+    <t>Cab Name</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>Xylo, Ertiga</t>
+  </si>
+  <si>
+    <t>37965</t>
+  </si>
+  <si>
+    <t>4.1/5</t>
+  </si>
+  <si>
+    <t>52742</t>
+  </si>
+  <si>
+    <t>4.2/5</t>
+  </si>
+  <si>
+    <t>Innova Crysta</t>
+  </si>
+  <si>
+    <t>72424</t>
+  </si>
+  <si>
+    <t>GiftCardTitles</t>
+  </si>
+  <si>
+    <t>Wedding Gift Card</t>
+  </si>
+  <si>
+    <t>Wedding Gift Envelope</t>
+  </si>
+  <si>
+    <t>Wedding Gift Box</t>
+  </si>
+  <si>
+    <t>Best Wishes Gift Card</t>
+  </si>
+  <si>
+    <t>Birthday Card</t>
+  </si>
+  <si>
+    <t>Thank You Gift Card</t>
+  </si>
+  <si>
+    <t>Congratulations Gift Card</t>
+  </si>
+  <si>
+    <t>Farewell Gift Card</t>
+  </si>
+  <si>
+    <t>Rakshabandhan Gift Card</t>
+  </si>
+  <si>
+    <t>Anniversary Gift Card</t>
+  </si>
+  <si>
+    <t>Staycation Gift Card</t>
+  </si>
+  <si>
+    <t>Luxury Hotels Gift Card</t>
+  </si>
+  <si>
+    <t>Mother's Day Gift Card</t>
+  </si>
+  <si>
+    <t>Father's Day Gift Card</t>
+  </si>
+  <si>
+    <t>Valentines Day Gift Card</t>
+  </si>
+  <si>
+    <t>Eid Mubarak Gift Card</t>
+  </si>
+  <si>
+    <t>Onam Gift Card</t>
+  </si>
+  <si>
+    <t>Christmas Gift Card</t>
+  </si>
+  <si>
+    <t>Karvachauth Gift Card</t>
+  </si>
+  <si>
+    <t>Happy New Year Gift Card</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Bhaidoojh Gift Card</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Diwali Gift Card</t>
+  </si>
+  <si>
+    <t>Rs. 16,267</t>
   </si>
 </sst>
 </file>
@@ -628,9 +735,9 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -638,19 +745,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2">
@@ -658,19 +759,13 @@
         <v>2</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>18</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
@@ -678,19 +773,13 @@
         <v>6</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>18</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
@@ -698,339 +787,13 @@
         <v>7</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>65</v>
-      </c>
-      <c r="F8" t="s" s="0">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="F9" t="s" s="0">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E10" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="F10" t="s" s="0">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E11" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="F11" t="s" s="0">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C12" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E12" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="F12" t="s" s="0">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C13" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D13" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E13" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="F13" t="s" s="0">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C14" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D14" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E14" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="F14" t="s" s="0">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="B15" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C15" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D15" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E15" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="F15" t="s" s="0">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="B16" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C16" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D16" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E16" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="F16" t="s" s="0">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
-        <v>45</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D17" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E17" t="s" s="0">
-        <v>46</v>
-      </c>
-      <c r="F17" t="s" s="0">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E18" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="F18" t="s" s="0">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="0">
-        <v>48</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D19" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E19" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="F19" t="s" s="0">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="0">
-        <v>50</v>
-      </c>
-      <c r="B20" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="C20" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="D20" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="E20" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="F20" t="s" s="0">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1038,7 +801,631 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/ExcelData/GoibiboReport.xlsx
+++ b/ExcelData/GoibiboReport.xlsx
@@ -13,17 +13,17 @@
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CabsList" r:id="rId8" sheetId="18"/>
-    <sheet name="GiftCardsList" r:id="rId9" sheetId="19"/>
-    <sheet name="CheapestFlights" r:id="rId7" sheetId="20"/>
-    <sheet name="TimeBasedResults" r:id="rId10" sheetId="21"/>
+    <sheet name="CabsList" r:id="rId8" sheetId="22"/>
+    <sheet name="GiftCardsList" r:id="rId9" sheetId="23"/>
+    <sheet name="CheapestFlights" r:id="rId7" sheetId="24"/>
+    <sheet name="TimeBasedResults" r:id="rId10" sheetId="25"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2878" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3090" uniqueCount="114">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -735,7 +735,7 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -801,7 +801,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -995,7 +995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -1417,7 +1417,7 @@
         <v>15</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1425,7 +1425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/ExcelData/GoibiboReport.xlsx
+++ b/ExcelData/GoibiboReport.xlsx
@@ -15,15 +15,15 @@
   <sheets>
     <sheet name="CabsList" r:id="rId8" sheetId="22"/>
     <sheet name="GiftCardsList" r:id="rId9" sheetId="23"/>
-    <sheet name="CheapestFlights" r:id="rId7" sheetId="24"/>
-    <sheet name="TimeBasedResults" r:id="rId10" sheetId="25"/>
+    <sheet name="CheapestFlights" r:id="rId7" sheetId="26"/>
+    <sheet name="TimeBasedResults" r:id="rId10" sheetId="27"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3090" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3240" uniqueCount="114">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -995,7 +995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -1417,7 +1417,7 @@
         <v>15</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1425,7 +1425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
